--- a/information_request_forms/014_the_idea_filter_form--information_request_forms.xlsx
+++ b/information_request_forms/014_the_idea_filter_form--information_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'in_development'}</t>
+          <t>in_development</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'In Development'}</t>
+          <t>In Development</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'information_requests'}</t>
+          <t>information_requests</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Information Requests'}</t>
+          <t>Information Requests</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'feedback'}</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Feedback'}</t>
+          <t>Feedback</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'support'}</t>
+          <t>support</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Support'}</t>
+          <t>Support</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'information_requests'}</t>
+          <t>information_requests</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Information Requests'}</t>
+          <t>Information Requests</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'feedback'}</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Feedback'}</t>
+          <t>Feedback</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'support'}</t>
+          <t>support</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Support'}</t>
+          <t>Support</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'not_started'}</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Not Started'}</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'done'}</t>
+          <t>done</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Done'}</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
